--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/01. Báo giá bảo hành/BG_.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/01. Báo giá bảo hành/BG_.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 03\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6E0191-59E3-4790-869A-7773F7E28E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF85ABDC-04AF-4C5B-A40D-45D81DC1FEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,21 +16,18 @@
     <sheet name="BG" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$J$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">BG!$A$1:$J$26</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
   <si>
-    <t>Model</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -76,9 +73,6 @@
     <t>Người Lập</t>
   </si>
   <si>
-    <t>Mô Tả Linh Kiện Thay Thế</t>
-  </si>
-  <si>
     <t>Đơn Vị Tính</t>
   </si>
   <si>
@@ -94,10 +88,20 @@
     <t>Xác Định Lỗi</t>
   </si>
   <si>
+    <t>Tổng</t>
+  </si>
+  <si>
+    <t>Mô Tả Linh 
+Kiện Thay Thế</t>
+  </si>
+  <si>
+    <t>Hà Nội, ngày  tháng  năm 202</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tên cty/ cá nhân: </t>
   </si>
   <si>
-    <t>Hà Nội, ngày   tháng   năm 202</t>
+    <t>Model/ Mã linh kiện</t>
   </si>
 </sst>
 </file>
@@ -202,7 +206,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,6 +216,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -360,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -403,9 +413,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -418,30 +425,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="8"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="10"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="11"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="10"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="14"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="14"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="13"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="13"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -452,9 +444,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -463,6 +452,69 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="13"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -478,65 +530,32 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -560,13 +579,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>233166</xdr:colOff>
+      <xdr:colOff>233165</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>168517</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1069731</xdr:colOff>
+      <xdr:colOff>1099039</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>51287</xdr:rowOff>
     </xdr:to>
@@ -597,8 +616,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="233166" y="168517"/>
-          <a:ext cx="2155411" cy="527539"/>
+          <a:off x="233165" y="168517"/>
+          <a:ext cx="2155412" cy="527539"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -897,15 +916,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA43"/>
+  <dimension ref="A1:AA45"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="3" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" style="3" customWidth="1" outlineLevel="1"/>
     <col min="9" max="9" width="12.140625" style="3" customWidth="1" outlineLevel="1"/>
@@ -919,189 +938,189 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41"/>
-      <c r="B1" s="42"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="51" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="53"/>
+      <c r="A1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="44"/>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="48" t="s">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="40"/>
+    </row>
+    <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="34"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="50"/>
-    </row>
-    <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="44"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="54" t="s">
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="46"/>
+    </row>
+    <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="36"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="56"/>
-    </row>
-    <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="57" t="s">
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="49"/>
+    </row>
+    <row r="5" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="59"/>
-    </row>
-    <row r="5" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="38"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="11"/>
+      <c r="A6" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="22"/>
+      <c r="G6" s="20"/>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
-      <c r="J6" s="29" t="s">
-        <v>24</v>
+      <c r="J6" s="23" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
+      <c r="A7" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="22"/>
+      <c r="G7" s="20"/>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>
     </row>
     <row r="8" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
+      <c r="A8" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" s="24"/>
+        <v>1</v>
+      </c>
+      <c r="G8" s="21"/>
       <c r="H8" s="8"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8"/>
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
+      <c r="A9" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
-      <c r="G9" s="24"/>
+      <c r="G9" s="21"/>
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
       <c r="AA9" s="2"/>
     </row>
     <row r="10" spans="1:27" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="30" t="s">
+      <c r="B10" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="G10" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="I10" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="J10" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="I10" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="30" t="s">
-        <v>21</v>
-      </c>
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="A11" s="59"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="60"/>
       <c r="F11" s="15"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="60"/>
       <c r="F12" s="15"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
@@ -1111,10 +1130,10 @@
     </row>
     <row r="13" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="16"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="7"/>
-      <c r="E13" s="15"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="15"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -1123,168 +1142,191 @@
       <c r="AA13" s="2"/>
     </row>
     <row r="14" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="14"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
+      <c r="A15" s="61" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="63"/>
       <c r="J15" s="29"/>
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="14"/>
+      <c r="AA16" s="2"/>
+    </row>
+    <row r="17" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="23"/>
+      <c r="AA17" s="2"/>
+    </row>
+    <row r="18" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="AA16" s="2"/>
-    </row>
-    <row r="17" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="32"/>
-      <c r="AA17" s="2"/>
-    </row>
-    <row r="18" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="35"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
       <c r="AA18" s="2"/>
     </row>
     <row r="19" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
+      <c r="A19" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="58"/>
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="27"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G20" s="24"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
       <c r="AA20" s="2"/>
     </row>
     <row r="21" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="27"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
       <c r="AA21" s="2"/>
     </row>
     <row r="22" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="27"/>
+      <c r="A22" s="22"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="24"/>
+      <c r="F22" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="21"/>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
       <c r="AA22" s="2"/>
     </row>
     <row r="23" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="17"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
       <c r="G23" s="21"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
       <c r="AA23" s="2"/>
     </row>
     <row r="24" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="25" spans="1:27" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="F25" s="4"/>
+    <row r="25" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="56" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="16"/>
       <c r="AA25" s="2"/>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
       <c r="AA26" s="2"/>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="F27" s="4"/>
       <c r="AA27" s="2"/>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
@@ -1335,19 +1377,32 @@
     <row r="43" spans="27:27" x14ac:dyDescent="0.25">
       <c r="AA43" s="2"/>
     </row>
+    <row r="44" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA44" s="2"/>
+    </row>
+    <row r="45" spans="27:27" x14ac:dyDescent="0.25">
+      <c r="AA45" s="2"/>
+    </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="10">
+  <mergeCells count="17">
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="D2:J2"/>
     <mergeCell ref="D1:J1"/>
     <mergeCell ref="D3:J3"/>
     <mergeCell ref="D4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
